--- a/docs/current-implementation-matrix.xlsx
+++ b/docs/current-implementation-matrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="Rc9e35254a22d4887"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="Rffa6906764564c63"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2420,28 +2420,28 @@
         <x:v>ships</x:v>
       </x:c>
       <x:c r="C55" s="12" t="str">
-        <x:v>Power-plant output and waste-heat calculation</x:v>
+        <x:v>Open-cycle reactor mass, cap, and compact power presentation</x:v>
       </x:c>
       <x:c r="D55" s="12" t="str">
-        <x:v>Delivered load × (1 - efficiency), which understates input minus output</x:v>
+        <x:v>Open-cycle drive load is presented as reactor electricity; plant mass, cost, output, and heat use one undifferentiated demand.</x:v>
       </x:c>
       <x:c r="E55" s="12" t="str">
         <x:v>No maintained-main override</x:v>
       </x:c>
       <x:c r="F55" s="12" t="str">
-        <x:v>Closed-cycle loads use delivered load × (1 / efficiency - 1). Open-cycle drives require reactor output Q = D / (1 - f × (1 - efficiency)) after hull-art scaling and retain Q - D as ship heat. Plant mass, cost, live generation, compatibility, reactor-bay use, designer display, and combat heat share that demand; powered-weapon module losses remain on the generator-sized burst interval.</x:v>
+        <x:v>Open-cycle drive demand D remains useful thermal GWth; closed-cycle drive and auxiliary demands remain electrical GWe. Gross reactor input is Qoc = D / (1 - f × (1 - efficiency)) plus electrical thermal input. Plant mass, build cost, and reactor-bay occupancy use Pmass = m × Qoc + Qelectrical, while drive cap use is Cdrive = m × Qoc for open cycle and D for closed cycle. Live thermal output and heat retain full energy conservation. As a temporary gameplay calibration pending the reactor rebalance, every reactor class except fuel-cell/general uses a 0.5 open-cycle multiplier; fuel-cell/general plants remain 1.0. The compact UI preserves vanilla Classification, Mass, Crew, Efficiency, Max Output To Drive, and cost rows; replaces installed Output with Electrical Output plus useful Thermal Output D only for open-cycle drives; collapses heat to one Waste Heat row; appends m parenthetically to Specific Power; and keeps reactor-bay volume outside the table.</x:v>
       </x:c>
       <x:c r="G55" s="12" t="str">
-        <x:v>shipBalance.enabled;shipBalance.correctPowerPlantWasteHeat;shipBalance.openCycleResidualHeatEnabled;shipBalance.openCycleDriveHeatFraction</x:v>
+        <x:v>shipBalance.enabled;shipBalance.correctPowerPlantWasteHeat;shipBalance.openCycleResidualHeatEnabled;shipBalance.openCycleDriveHeatFraction;shipBalance.openCycleThermalMassScalingEnabled</x:v>
       </x:c>
       <x:c r="H55" s="12" t="str">
-        <x:v>BalancePatches.cs:PowerPlantWasteHeatPatch;BalancePatches.cs:OpenCycleDrivePowerPlantCompatibilityPatch;BalancePatches.cs:OpenCycleValidDrivesForPowerPlantsPatch;ShipPowerPatches.cs:InstalledDriveHeatPatch;ShipPowerPatches.cs:PoweredWeaponRadiatorHeatPatch;ShipPowerPatches.cs:AuxiliaryElectricalGenerationPatch;ShipPowerPatches.cs:GeneratedPowerHeatPatch;ShipPowerPatches.cs:DuplicateSystemsHeatPatch;ShipPowerPatches.cs:WeaponHeatCapacityPrecheckPatch;Core/PowerPlantThermalMath.cs;Core/WeaponPowerMath.cs;docs/ship-balance-research/open-cycle-reactor-demand-and-heat.md</x:v>
+        <x:v>Core/PowerPlantThermalMath.cs;Core/PowerPlantScalingMath.cs;Core/PowerPlantScalingRegistry.cs;BalancePatches.cs:ShipPowerDemandFeature;BalancePatches.cs:PowerPlantWasteHeatPatch;BalancePatches.cs:SeparatedShipPowerProductionPatch;BalancePatches.cs:OpenCyclePowerPlantMassPatch;BalancePatches.cs:OpenCyclePowerPlantCostPatch;BalancePatches.cs:OpenCycleDrivePowerPlantCompatibilityPatch;BalancePatches.cs:OpenCycleValidDrivesForPowerPlantsPatch;ShipPowerPatches.cs:InstalledDriveHeatPatch;ShipPowerPatches.cs:PoweredWeaponRadiatorHeatPatch;ShipPowerPatches.cs:AuxiliaryElectricalGenerationPatch;ShipPowerPatches.cs:GeneratedPowerHeatPatch;ShipPowerPatches.cs:DuplicateSystemsHeatPatch;ShipPowerPatches.cs:WeaponHeatCapacityPrecheckPatch;TIPowerPlantTemplate.json;UIGeneralControls.en;docs/ship-balance-research/open-cycle-reactor-demand-and-heat.md;docs/ship-balance-research/open-cycle-reactor-mass-scaling-plan-2026-08-21.md</x:v>
       </x:c>
       <x:c r="I55" s="12" t="str">
-        <x:v>updated</x:v>
+        <x:v>implemented</x:v>
       </x:c>
       <x:c r="J55" s="12" t="str">
-        <x:v>Open-cycle reactor demand now conserves useful drive work plus the configured retained loss. Combat burns use the installed ship-level demand, fixing the raw drive-template bypass of hull-art scaling. Candidate and static AI filters enforce the same output boundary. Radiators still cover corrected reactor rejection and explicit weapon-conversion losses exactly once.</x:v>
+        <x:v>All non-fuel-cell/general open-cycle propulsion is temporarily mass- and cap-rated at 50% of gross thermal input so the uneven pre-rebalance reactor progression cannot amplify technology-specific discounts. Authored maxOutput_GW values remain unchanged: 8 GWth open-cycle and 4 GWe closed-cycle each consume 4 GW of rated drive capacity at m = 0.5 before retained-loss correction. Thermal Output in the UI deliberately means useful work D delivered to the open-cycle drive; gross Qoc remains internal.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="39.599998474121094" hidden="0" customHeight="1">
@@ -3930,7 +3930,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f1854c3dc04442e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52ff3a65611a4e34"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/current-implementation-matrix.xlsx
+++ b/docs/current-implementation-matrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="Rffa6906764564c63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="R82d81f10c7434dc4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -461,8 +461,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImplementationMatrix" displayName="ImplementationMatrix" ref="A1:J101" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:J101"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImplementationMatrix" displayName="ImplementationMatrix" ref="A1:J102" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:J102"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="feature_id"/>
     <x:tableColumn id="2" name="category"/>
@@ -3916,6 +3916,38 @@
         <x:v>One orbital hab has 3.33% of native ambient-hazard weight, 15 have 50%, and 30+ have 100%. Orbital Debris Strike, forced mission-control malfunctions, sabotage, revolt, smuggling, containment, and combat remain unchanged. The native Meteor Strike and Hab Accident templates combine orbital and surface targets, so the adjustment occurs at their pre-target global selection step.</x:v>
       </x:c>
     </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="str">
+        <x:v>hab_upgrade_boost_substitution</x:v>
+      </x:c>
+      <x:c r="B102" t="str">
+        <x:v>habs</x:v>
+      </x:c>
+      <x:c r="C102" t="str">
+        <x:v>Hab-upgrade Boost substitution</x:v>
+      </x:c>
+      <x:c r="D102" t="str">
+        <x:v>The installed-module Upgrade preview tests only the unsubstituted space-resource quote, while individual placement and bulk execution independently retry with Boost substitution.</x:v>
+      </x:c>
+      <x:c r="E102" t="str">
+        <x:v>No maintained-main override.</x:v>
+      </x:c>
+      <x:c r="F102" t="str">
+        <x:v>One shared upgrade-cost resolver prefers an affordable native space quote, otherwise an affordable Boost-substituted quote, and otherwise preserves the native shortage. Single-upgrade preview, placement, and bulk execution all use it.</x:v>
+      </x:c>
+      <x:c r="G102" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="H102" t="str">
+        <x:v>HabUpgradeCostPatches.cs:HabUpgradePreviewCostPatch;HabUpgradeCostPatches.cs:HabUpgradePlacementCostPatch;HabUpgradeCostPatches.cs:HabUpgradeBulkExecutionCostPatch;HabUpgradeCostPatches.cs:HabUpgradeCostResolver;tools/validate-hab-upgrade-cost-patches.ps1;docs/compatibility/ti-1.0.53-hab-upgrade-affordability.md</x:v>
+      </x:c>
+      <x:c r="I102" t="str">
+        <x:v>updated</x:v>
+      </x:c>
+      <x:c r="J102" t="str">
+        <x:v>TI 1.0.53 exposed the parallel implementations when Upgrade All accepted a mixed stockpile/Boost route but the individual Upgrade button remained grey. Guarded rewrites cover exactly two preview and two bulk-execution upgrade quotes; the placement helper is replaced as one unit.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="I2:I38">
@@ -3930,7 +3962,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52ff3a65611a4e34"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4aadafefd16b4cf0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/current-implementation-matrix.xlsx
+++ b/docs/current-implementation-matrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="R82d81f10c7434dc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="Re457e96a5cfe432d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2781,19 +2781,19 @@
         <x:v>No maintained-main override</x:v>
       </x:c>
       <x:c r="F66" s="11" t="str">
-        <x:v>Gun power is runtime template metadata and adds no save field. On load, ship power statistics use current templates and current mass is reconciled to recalculated dry mass plus saved propellant</x:v>
+        <x:v>Gun power is runtime template metadata and adds no save field. On load, saved faction designs rebuild dry mass, acceleration, delta-v, battery, and heat through the game's aggregate template cache function; instantiated ships use that same refresh before reconciling current mass to recalculated dry mass plus saved propellant.</x:v>
       </x:c>
       <x:c r="G66" s="11" t="str">
         <x:v>shipBalance.enabled</x:v>
       </x:c>
       <x:c r="H66" s="11" t="str">
-        <x:v>GunPowerRegistry.cs;ShipPowerPatches.cs:GunPowerTemplateInitializationPatch;ShipPowerPatches.cs:ShipPowerSaveLoadCachePatch;Main.cs:Main</x:v>
+        <x:v>GunPowerRegistry.cs;ShipPowerPatches.cs:GunPowerTemplateInitializationPatch;ShipPowerPatches.cs:ShipPowerSaveLoadCachePatch;Main.cs:Main;ShipPowerPatches.cs:ShipDesignPerformanceSaveLoadCachePatch</x:v>
       </x:c>
       <x:c r="I66" s="11" t="str">
         <x:v>implemented</x:v>
       </x:c>
       <x:c r="J66" s="11" t="str">
-        <x:v>The registry is rebuilt from active load-ordered mod JSON before a save is selected. TI 1.0.51 late saves retain their saved fuel while propulsion is marked for recalculation, and mixed conventional-gun unlock sets initialize without a module-table exception. Disabling or removing the mod requires no custom save payload.</x:v>
+        <x:v>The registry is rebuilt from active load-ordered mod JSON before a save is selected. TI 1.0.51 late saves retain their saved fuel while propulsion is marked for recalculation, and mixed conventional-gun unlock sets initialize without a module-table exception. Disabling or removing the mod requires no custom save payload. TI 1.0.53 faction designs now refresh every performance cache after save registration, preventing one cached statistic from retaining an older mass model.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="13.5" hidden="0" customHeight="1">
@@ -3421,19 +3421,19 @@
         <x:v>No measured per-art hull-volume fuel cap or hull/engine art-pane readout</x:v>
       </x:c>
       <x:c r="F86" s="12" t="str">
-        <x:v>Measured per-art main-hull volume minus installed utility/weapon footprints and 50 m³ per total fitted crew billet; density-aware 100-ton tanks clamp before designer refresh and save. Human AI designs select an appearance before propulsion sizing, ideal-tank calculations clamp to capacity and recompute achieved delta-v, refits preserve their appearance, and final human/alien/STO save boundaries reject illegal propulsion layouts. The art pane shows selected-art De Laval and Magnetic gameplay scales, Pulsed 1x, measured engine-bay volume, flat empty-hull mass, base repair crew, propellant, tank cap, and usable fuel volume.</x:v>
+        <x:v>Measured per-art main-hull volume minus installed utility/weapon footprints and 50 m³ per total fitted crew billet; density-aware 100-ton tanks clamp during normal designer refresh and save. Existing-template loading preserves the serialized tank count while the UI is assembled, then checks it once against the final saved art and rebuilds cost and performance caches. Human AI designs select an appearance before propulsion sizing, ideal-tank calculations clamp to capacity and recompute achieved delta-v, refits preserve their appearance, and final human/alien/STO save boundaries reject illegal propulsion layouts. The art pane shows selected-art De Laval and Magnetic gameplay scales, Pulsed 1x, measured engine-bay volume, flat empty-hull mass, base repair crew, propellant, tank cap, and usable fuel volume.</x:v>
       </x:c>
       <x:c r="G86" s="12" t="str">
         <x:v>shipBalance.enabled;shipBalance.fuelVolumeCapacityEnabled;shipBalance.utilitySlotVolume_m3;shipBalance.hullWeaponSlotVolume_m3;shipBalance.noseWeaponSlotVolume_m3;shipBalance.crewPressurizedVolume_m3</x:v>
       </x:c>
       <x:c r="H86" s="12" t="str">
-        <x:v>FuelCapacityPatches.cs:PropellantDensityTemplateInitializationPatch;FuelCapacityPatches.cs:FuelCapacityDesignerRefreshPatch;FuelCapacityPatches.cs:FuelCapacitySpinnerLabelPatch;FuelCapacityPatches.cs:FuelCapacitySaveGuardPatch;FuelCapacityPatches.cs:AiShipDesignCapacityBoundaryPatch;FuelCapacityPatches.cs:AiShipRefitCapacityBoundaryPatch;FuelCapacityPatches.cs:AiShipEarlyAppearanceSelectionPatch;FuelCapacityPatches.cs:FuelCapacityIdealTankCountPatch;FuelCapacityPatches.cs:AlienShipFuelCapacityPatch;FuelCapacityPatches.cs:StoFighterFuelCapacityPatch;FuelCapacityPatches.cs:SavedShipCapacityInvariantPatch;Core/HullVolumeCatalog.cs:HullVolumeCatalog;Core/HullDriveScaleCatalog.cs:HullDriveScaleCatalog;Core/PropellantDensityRegistry.cs:PropellantDensityRegistry;Config/hull-variant-main-volumes.csv;Config/hull-variant-drive-scales.csv</x:v>
+        <x:v>FuelCapacityPatches.cs:PropellantDensityTemplateInitializationPatch;FuelCapacityPatches.cs:FuelCapacityDesignerRefreshPatch;FuelCapacityPatches.cs:FuelCapacitySpinnerLabelPatch;FuelCapacityPatches.cs:FuelCapacitySaveGuardPatch;FuelCapacityPatches.cs:AiShipDesignCapacityBoundaryPatch;FuelCapacityPatches.cs:AiShipRefitCapacityBoundaryPatch;FuelCapacityPatches.cs:AiShipEarlyAppearanceSelectionPatch;FuelCapacityPatches.cs:FuelCapacityIdealTankCountPatch;FuelCapacityPatches.cs:AlienShipFuelCapacityPatch;FuelCapacityPatches.cs:StoFighterFuelCapacityPatch;FuelCapacityPatches.cs:SavedShipCapacityInvariantPatch;Core/HullVolumeCatalog.cs:HullVolumeCatalog;Core/HullDriveScaleCatalog.cs:HullDriveScaleCatalog;Core/PropellantDensityRegistry.cs:PropellantDensityRegistry;Config/hull-variant-main-volumes.csv;Config/hull-variant-drive-scales.csv;FuelCapacityPatches.cs:ExistingShipFuelCapacityLoadPatch</x:v>
       </x:c>
       <x:c r="I86" s="12" t="str">
         <x:v>implemented</x:v>
       </x:c>
       <x:c r="J86" s="12" t="str">
-        <x:v>Default footprints are 200 m³ per utility cell, 250 m³ per hull-weapon cell, and 400 m³ per nose-weapon cell. Fuel capacity reserves total fitted crew; the overlay's repair crew is the hull template base complement. De Laval and Magnetic values are the same measured x6 art-envelope ratios consumed by gameplay; Pulsed remains explicitly 1x. Guarded alien and STO transpilers require their exact expected tank-assignment counts and throw rather than allowing a partial patch.</x:v>
+        <x:v>Default footprints are 200 m³ per utility cell, 250 m³ per hull-weapon cell, and 400 m³ per nose-weapon cell. Fuel capacity reserves total fitted crew; the overlay's repair crew is the hull template base complement. De Laval and Magnetic values are the same measured x6 art-envelope ratios consumed by gameplay; Pulsed remains explicitly 1x. Guarded alien and STO transpilers require their exact expected tank-assignment counts and throw rather than allowing a partial patch. The staged Upgrade load no longer lets a lower-capacity intermediate art discard tanks that are legal on the saved appearance.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="150" customHeight="1">
@@ -3962,7 +3962,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4aadafefd16b4cf0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7860713ffeef423b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/current-implementation-matrix.xlsx
+++ b/docs/current-implementation-matrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="Re457e96a5cfe432d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="R85b5cb40221d4249"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2563,13 +2563,13 @@
         <x:v>shipBalance.enabled;shipBalance.crewSupportMassEnabled;shipBalance.crewSupportMass_tons;shipBalance.hullDriveScalingEnabled</x:v>
       </x:c>
       <x:c r="H59" s="11" t="str">
-        <x:v>TIShipHullTemplate.json;BalancePatches.cs:ShipCrewSupportMassPatch;BalancePatches.cs:HullScaledDriveThrustPatch;BalancePatches.cs:HullScaledLiveShipThrustPatch;BalancePatches.cs:HullScaledDrivePowerPatch;BalancePatches.cs:HullScaledDriveMassPatch;BalancePatches.cs:HullVariantEmptyMassPatch;BalancePatches.cs:HullScaledDriveConstructionCostPatch;BalancePatches.cs:HullScaledDriveRefitCostPatch;BalancePatches.cs:HullScaledDriveCompatibilityPatch;BalancePatches.cs:HullScaledPowerPlantCompatibilityPatch;ShipPowerPatches.cs:ShipModuleEnergyColumnCompatibilityPatch;ShipPowerPatches.cs:HullScaledDriveDescriptionPatch;ShipPowerPatches.cs:HullScaledDriveTooltipPatch;ShipPowerPatches.cs:HullScaledDriveTableRefreshPatch;Core/HullDriveScaleCatalog.cs:HullDriveScaleCatalog;Core/ShipBalanceMath.cs;Config/hull-variant-drive-scales.csv;scripts/ship-balance/measure_ship_prefabs.py;docs/ship-balance-research/human-drive-art-scaling-and-structural-mass-plan.md</x:v>
+        <x:v>TIShipHullTemplate.json;BalancePatches.cs:ShipCrewSupportMassPatch;BalancePatches.cs:HullScaledDriveThrustPatch;BalancePatches.cs:HullScaledLiveShipThrustPatch;BalancePatches.cs:HullScaledDrivePowerPatch;BalancePatches.cs:HullScaledDriveMassPatch;BalancePatches.cs:HullVariantEmptyMassPatch;BalancePatches.cs:HullScaledDriveConstructionCostPatch;BalancePatches.cs:HullScaledDriveRefitCostPatch;BalancePatches.cs:HullScaledDriveCompatibilityPatch;BalancePatches.cs:HullScaledPowerPlantCompatibilityPatch;ShipPowerPatches.cs:ShipModuleEnergyColumnCompatibilityPatch;ShipPowerPatches.cs:HullScaledDriveDescriptionPatch;ShipPowerPatches.cs:HullScaledDriveTooltipPatch;ShipPowerPatches.cs:HullScaledDriveTableRefreshPatch;Core/HullDriveScaleCatalog.cs:HullDriveScaleCatalog;Core/ShipBalanceMath.cs;Config/hull-variant-drive-scales.csv;scripts/ship-balance/measure_ship_prefabs.py;docs/ship-balance-research/human-drive-art-scaling-and-structural-mass-plan.md;ShipPowerPatches.cs:HullVariantMassTooltipPatch</x:v>
       </x:c>
       <x:c r="I59" s="11" t="str">
         <x:v>updated</x:v>
       </x:c>
       <x:c r="J59" s="11" t="str">
-        <x:v>The runtime and art selector share the measured catalog for all 48 human appearances and both conventional nozzle families, including factors below 1x. Pulsed is always 1x. Flat appearance masses are listed in the implementation plan; appearance 0 preserves the current template mass. Reactor-bay compatibility and appearance reconciliation consume the same scaled candidate demand.</x:v>
+        <x:v>The runtime and art selector share the measured catalog for all 48 human appearances and both conventional nozzle families, including factors below 1x. Pulsed is always 1x. Flat appearance masses are listed in the implementation plan; appearance 0 preserves the current template mass. Reactor-bay compatibility and appearance reconciliation consume the same scaled candidate demand. Wet-mass hull tons and percentage use the selected appearance.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -3962,7 +3962,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7860713ffeef423b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f2946c0c39c4dff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/current-implementation-matrix.xlsx
+++ b/docs/current-implementation-matrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="R85b5cb40221d4249"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="R61de976e52114f5c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -461,8 +461,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImplementationMatrix" displayName="ImplementationMatrix" ref="A1:J102" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:J102"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImplementationMatrix" displayName="ImplementationMatrix" ref="A1:J103" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:J103"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="feature_id"/>
     <x:tableColumn id="2" name="category"/>
@@ -748,7 +748,7 @@
         <x:v>Built and IL-validated against the installed TI 1.0.51 assemblies. Runtime toggles return prefixes to vanilla and make transpiler helpers return live vanilla values.</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="36" hidden="0" customHeight="1">
+    <x:row r="3" ht="160" hidden="0" customHeight="1">
       <x:c r="A3" s="60" t="str">
         <x:v>investment_points</x:v>
       </x:c>
@@ -765,19 +765,19 @@
         <x:v>Small-country crutch curve</x:v>
       </x:c>
       <x:c r="F3" s="61" t="str">
-        <x:v>GDP / $100B with the configurable 70%-100% low-income ramp, followed by x1.05 output</x:v>
+        <x:v>Monthly gross IP = GDP/$100B × low-income multiplier × 1.10. After existing penalties and military upkeep, deduct 0.05 per installed MC + 0.10 per raw monthly Boost + 0.001 per raw monthly Funding; floor available IP at zero.</x:v>
       </x:c>
       <x:c r="G3" s="61" t="str">
-        <x:v>investment.enabled;investment.gdpPerInvestmentPointBillions;investment.lowIncomeMultiplierAtZero;investment.lowIncomeThreshold;investment.outputMultiplier</x:v>
+        <x:v>investment.enabled;investment.gdpPerInvestmentPointBillions;investment.lowIncomeMultiplierAtZero;investment.lowIncomeThreshold;investment.outputMultiplier;investment.spaceAssetUpkeepEnabled;investment.missionControlUpkeep;investment.boostUpkeep;investment.fundingUpkeep</x:v>
       </x:c>
       <x:c r="H3" s="61" t="str">
-        <x:v>NationalValuesPatches.cs:InvestmentPointsPatch</x:v>
+        <x:v>NationalValuesPatches.cs:InvestmentPointsPatch;NationalSpaceAssetPatches.cs:NationalSpaceAssetUpkeepPatch;Core/NationalSpaceAssetMath.cs</x:v>
       </x:c>
       <x:c r="I3" s="62" t="str">
-        <x:v>preserved</x:v>
+        <x:v>updated</x:v>
       </x:c>
       <x:c r="J3" s="61" t="str">
-        <x:v>Linear GDP-to-IP remains the scale authority; the new output factor raises every nation by exactly 5%.</x:v>
+        <x:v>0.9.8: outputMultiplier 1.10 and Moderate upkeep. Raw national assets are charged before federation sharing. Existing military deductions remain. No new save fields.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="120" hidden="0" customHeight="1">
@@ -1868,7 +1868,7 @@
         <x:v>The Economy getter supplies the displayed gain; the climate common-method patch keeps gameplay and display damage synchronized.</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="24" hidden="0" customHeight="1">
+    <x:row r="38" ht="100" hidden="0" customHeight="1">
       <x:c r="A38" s="57" t="str">
         <x:v>ui_investment</x:v>
       </x:c>
@@ -1885,7 +1885,7 @@
         <x:v>Whole-method replacement</x:v>
       </x:c>
       <x:c r="F38" s="58" t="str">
-        <x:v>Vanilla tooltip plus GDP/IP and army/navy upkeep section</x:v>
+        <x:v>IP tooltip uses native introductory prose and conditional adviser, occupation, Unrest, army, navy, MC, Boost and Funding bullets. Army rates/totals use actual runtime upkeep. Repair debt is a separate conditional paragraph. The duplicate diagnostic block is removed.</x:v>
       </x:c>
       <x:c r="G38" s="58" t="str">
         <x:v>ui.enabled;ui.expandedTooltips</x:v>
@@ -1897,7 +1897,7 @@
         <x:v>implemented</x:v>
       </x:c>
       <x:c r="J38" s="58" t="str">
-        <x:v>Postfix preserves upstream and vanilla text</x:v>
+        <x:v>Native bullet wording and base/available IP narrative retained. Omit absent or zero-cost categories. UI-only correction to 0.9.8.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="52.79999923706055" hidden="0" customHeight="1">
@@ -3946,6 +3946,38 @@
       </x:c>
       <x:c r="J102" t="str">
         <x:v>TI 1.0.53 exposed the parallel implementations when Upgrade All accepted a mixed stockpile/Boost route but the individual Upgrade button remained grey. Guarded rewrites cover exactly two preview and two bulk-execution upgrade quotes; the placement helper is replaced as one unit.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="170" customHeight="1">
+      <x:c r="A103" s="12" t="str">
+        <x:v>national_boost_cap</x:v>
+      </x:c>
+      <x:c r="B103" s="12" t="str">
+        <x:v>national economy</x:v>
+      </x:c>
+      <x:c r="C103" s="12" t="str">
+        <x:v>National Boost production cap</x:v>
+      </x:c>
+      <x:c r="D103" s="12" t="str">
+        <x:v>Boost production has no GDP capacity cap.</x:v>
+      </x:c>
+      <x:c r="E103" s="12" t="str">
+        <x:v>No national Boost cap.</x:v>
+      </x:c>
+      <x:c r="F103" s="12" t="str">
+        <x:v>Monthly Boost cap = 2 × GDP_billions / max(200, 300 - 6 × Education). Preserve existing over-cap production; block new growth until capacity rises. Final positive increment is limited to remaining headroom.</x:v>
+      </x:c>
+      <x:c r="G103" s="12" t="str">
+        <x:v>investment.enabled;investment.boostCapEnabled;investment.boostCapFactor</x:v>
+      </x:c>
+      <x:c r="H103" s="12" t="str">
+        <x:v>NationalSpaceAssetPatches.cs:BoostCapPriorityPatch;NationalSpaceAssetPatches.cs:BoostCapFacilityPatch;NationalSpaceAssetPatches.cs:BoostCapDirectInvestmentPatch;NationalSpaceAssetPatches.cs:BoostCapEconomicChangePatch;Core/NationalSpaceAssetMath.cs;NationalSpaceAssetUiPatches.cs:NationalBoostValuePatch;NationalSpaceAssetUiPatches.cs:NationalBoostTooltipPatch</x:v>
+      </x:c>
+      <x:c r="I103" s="12" t="str">
+        <x:v>implemented</x:v>
+      </x:c>
+      <x:c r="J103" s="12" t="str">
+        <x:v>Shared validity gates construction. Nation panel shows current (maximum) Boost, preserving the native trend arrow. Tooltip describes those two values like MC and retains the 31-day change. Existing over-cap production is preserved.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3962,7 +3994,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f2946c0c39c4dff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R695427c6b7894a6d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/current-implementation-matrix.xlsx
+++ b/docs/current-implementation-matrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="R61de976e52114f5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="R64c3fdfbd98a4040"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -461,8 +461,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImplementationMatrix" displayName="ImplementationMatrix" ref="A1:J103" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:J103"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImplementationMatrix" displayName="ImplementationMatrix" ref="A1:J106" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:J106"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="feature_id"/>
     <x:tableColumn id="2" name="category"/>
@@ -3980,6 +3980,102 @@
         <x:v>Shared validity gates construction. Nation panel shows current (maximum) Boost, preserving the native trend arrow. Tooltip describes those two values like MC and retains the 31-day change. Existing over-cap production is preserved.</x:v>
       </x:c>
     </x:row>
+    <x:row r="104" ht="260" customHeight="1">
+      <x:c r="A104" s="12" t="str">
+        <x:v>ship_capital_heavy_mounts</x:v>
+      </x:c>
+      <x:c r="B104" s="12" t="str">
+        <x:v>ships</x:v>
+      </x:c>
+      <x:c r="C104" s="12" t="str">
+        <x:v>Capital heavy hull mounts</x:v>
+      </x:c>
+      <x:c r="D104" s="12" t="str">
+        <x:v>Hull weapons consume 1, 2 or 4 cells on all hulls.</x:v>
+      </x:c>
+      <x:c r="E104" s="12" t="str">
+        <x:v>No maintained-main override.</x:v>
+      </x:c>
+      <x:c r="F104" s="12" t="str">
+        <x:v>Titan, AlienTitan and AlienMothership accept only FourHull weapons, one per cell. Smaller hull weapons are hidden in icon and table catalogs. Full heavy costs remain. Player and AI share eligibility.</x:v>
+      </x:c>
+      <x:c r="G104" s="12" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="H104" s="12" t="str">
+        <x:v>CapitalMountPatches.cs:CapitalWeaponFootprintPatch;CapitalMountPatches.cs:CapitalWeaponAvailabilityPatch;CapitalMountPatches.cs:CapitalWeaponAssignmentPatch;CapitalMountPatches.cs:CapitalWeaponDropPatch;CapitalMountPatches.cs:CapitalWeaponIconPatch;CapitalMountPatches.cs:CapitalWeaponModelAnchorPatch;CapitalMountPatches.cs:CapitalAiHullWeaponsPatch;CapitalMountPatches.cs:CapitalNewDesignSchemaPatch;CapitalMountPatches.cs:CapitalCloneSchemaPatch;CapitalMountPatches.cs:CapitalDesignValidationPatch;CapitalMountPatches.cs:CapitalCompleteDesignPatch;CapitalMountPatches.cs:CapitalSavedDesignGuardPatch;CapitalMountPatches.cs:CapitalRefitLayoutGuardPatch;CapitalMountPatches.cs:CapitalImportedDesignPatch;CapitalMountPatches.cs:CapitalWeaponCatalogPatch</x:v>
+      </x:c>
+      <x:c r="I104" s="12" t="str">
+        <x:v>implemented</x:v>
+      </x:c>
+      <x:c r="J104" s="12" t="str">
+        <x:v>0.10.0. Nose fittings and statistics unchanged; maximum-nose proposal deferred. Mothership uses a JSON-only layout inside the native designer grid; no bespoke row code.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="260" customHeight="1">
+      <x:c r="A105" s="12" t="str">
+        <x:v>ship_capital_migration</x:v>
+      </x:c>
+      <x:c r="B105" s="12" t="str">
+        <x:v>ships</x:v>
+      </x:c>
+      <x:c r="C105" s="12" t="str">
+        <x:v>Capital layout migration</x:v>
+      </x:c>
+      <x:c r="D105" s="12" t="str">
+        <x:v>No capital conversion schema.</x:v>
+      </x:c>
+      <x:c r="E105" s="12" t="str">
+        <x:v>No maintained-main override.</x:v>
+      </x:c>
+      <x:c r="F105" s="12" t="str">
+        <x:v>Schema 1 expands legacy 1/2/4-cell installations into 1/2/4 heavy weapons. Preserve damage, ammunition fractions, supported modes and existing fuel.</x:v>
+      </x:c>
+      <x:c r="G105" s="12" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="H105" s="12" t="str">
+        <x:v>CapitalMigrationPatches.cs:CapitalResolvedShipSchemaPatch;CapitalMigrationPatches.cs:CapitalMigrationLoadSourcePatch;CapitalMigrationPatches.cs:CapitalMigrationSaveGuardPatch;CapitalMigrationPatches.cs:CapitalCampaignMigrationPatch;CapitalMigrationPatches.cs:CapitalNewShipMigrationPatch;CapitalMigrationPatches.cs:CapitalCopiedShipSchemaPatch;Core/CapitalMountRuntime.cs;Core/CapitalMountPolicy.cs</x:v>
+      </x:c>
+      <x:c r="I105" s="12" t="str">
+        <x:v>implemented</x:v>
+      </x:c>
+      <x:c r="J105" s="12" t="str">
+        <x:v>New saves take priority. Migration archives source and report. Over-limit ships remain usable; refit copies restore limits. Missing unlocks use legacy equipment without research grants.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="260" customHeight="1">
+      <x:c r="A106" s="12" t="str">
+        <x:v>ship_capital_hull_capacity</x:v>
+      </x:c>
+      <x:c r="B106" s="12" t="str">
+        <x:v>ships</x:v>
+      </x:c>
+      <x:c r="C106" s="12" t="str">
+        <x:v>Capital utility, crew and bare hull mass</x:v>
+      </x:c>
+      <x:c r="D106" s="12" t="str">
+        <x:v>Original utility counts and hull masses.</x:v>
+      </x:c>
+      <x:c r="E106" s="12" t="str">
+        <x:v>No maintained-main override.</x:v>
+      </x:c>
+      <x:c r="F106" s="12" t="str">
+        <x:v>Dreadnoughts gain 1 utility, Titans 3, Motherships 4. Human Dreadnought/Titan crew 19/40; alien crew unchanged. V0 bare masses: Titan 3400, alien Dreadnought 2200, Titan 2600, Mothership 8500 t.</x:v>
+      </x:c>
+      <x:c r="G106" s="12" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="H106" s="12" t="str">
+        <x:v>TIShipHullTemplate.json;Core/ShipBalanceMath.cs;docs/ship-balance-research/capital-heavy-mount-implementation.md</x:v>
+      </x:c>
+      <x:c r="I106" s="12" t="str">
+        <x:v>implemented</x:v>
+      </x:c>
+      <x:c r="J106" s="12" t="str">
+        <x:v>Other large human appearances round bare hull plus base crew to 100 t. Slot indices and utility footprints preserved; Mothership layout fits the native grid entirely through JSON.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="I2:I38">
@@ -3994,7 +4090,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R695427c6b7894a6d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a5e918944f94d58"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/current-implementation-matrix.xlsx
+++ b/docs/current-implementation-matrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="R64c3fdfbd98a4040"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="R35cb905a5dfb45ef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2441,7 +2441,7 @@
         <x:v>implemented</x:v>
       </x:c>
       <x:c r="J55" s="12" t="str">
-        <x:v>All non-fuel-cell/general open-cycle propulsion is temporarily mass- and cap-rated at 50% of gross thermal input so the uneven pre-rebalance reactor progression cannot amplify technology-specific discounts. Authored maxOutput_GW values remain unchanged: 8 GWth open-cycle and 4 GWe closed-cycle each consume 4 GW of rated drive capacity at m = 0.5 before retained-loss correction. Thermal Output in the UI deliberately means useful work D delivered to the open-cycle drive; gross Qoc remains internal.</x:v>
+        <x:v>Release 0.10.1 doubles specificPower_tGW for all 27 human fusion reactors and explicitly sets Open cooling on all 174 human/alien fusion drive variants. Alien reactor masses remain unchanged. Retains the 0.5 open-cycle thermal mass/cap multiplier and 0.01 residual-loss parameter. Fitted reactor mass need not double because demand also moves to the direct thermal path. Manual designer and saved-ship checks remain pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="39.599998474121094" hidden="0" customHeight="1">
@@ -4090,7 +4090,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a5e918944f94d58"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R058176c4e10b4c73"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/current-implementation-matrix.xlsx
+++ b/docs/current-implementation-matrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="R35cb905a5dfb45ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="R447de19d2ecd4dbc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="16">
+  <x:fonts count="17">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -105,8 +105,13 @@
       <x:color rgb="FF375623"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="26">
+  <x:fills count="27">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -233,6 +238,11 @@
         <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -240,7 +250,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="72">
+  <x:cellXfs count="76">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -451,6 +461,14 @@
       <x:alignment horizontal="center" vertical="center" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -461,8 +479,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImplementationMatrix" displayName="ImplementationMatrix" ref="A1:J106" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:J106"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImplementationMatrix" displayName="ImplementationMatrix" ref="A1:J107" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:J107"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="feature_id"/>
     <x:tableColumn id="2" name="category"/>
@@ -4076,6 +4094,38 @@
         <x:v>Other large human appearances round bare hull plus base crew to 100 t. Slot indices and utility footprints preserved; Mothership layout fits the native grid entirely through JSON.</x:v>
       </x:c>
     </x:row>
+    <x:row r="107" ht="150" customHeight="1">
+      <x:c r="A107" s="75" t="str">
+        <x:v>alien_territory_demands</x:v>
+      </x:c>
+      <x:c r="B107" s="75" t="str">
+        <x:v>National politics</x:v>
+      </x:c>
+      <x:c r="C107" s="75" t="str">
+        <x:v>Alien demands require full Servant control</x:v>
+      </x:c>
+      <x:c r="D107" s="75" t="str">
+        <x:v>Native Demand Claim permits a willing executive to surrender a non-capital region.</x:v>
+      </x:c>
+      <x:c r="E107" s="75" t="str">
+        <x:v>No dedicated override.</x:v>
+      </x:c>
+      <x:c r="F107" s="75" t="str">
+        <x:v>0.10.2: Alien demands require Servant ownership of every control point in the target nation. Other factions and human demands retain native eligibility.</x:v>
+      </x:c>
+      <x:c r="G107" s="75" t="str">
+        <x:v>enabled</x:v>
+      </x:c>
+      <x:c r="H107" s="75" t="str">
+        <x:v>Patches/AlienTerritoryDemandPatches.cs:AlienTerritoryDemandTargetsPatch</x:v>
+      </x:c>
+      <x:c r="I107" s="75" t="str">
+        <x:v>implemented</x:v>
+      </x:c>
+      <x:c r="J107" s="75" t="str">
+        <x:v>Mixed or unowned points block new demands. Native claims and other gates remain. Assume Control and already queued demands are unchanged. See docs/alien-territory-demands.md. Manual testing pending.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="I2:I38">
@@ -4090,7 +4140,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R058176c4e10b4c73"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19c7c870f91347ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/current-implementation-matrix.xlsx
+++ b/docs/current-implementation-matrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="R447de19d2ecd4dbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="R85d6809df0054464"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4015,19 +4015,19 @@
         <x:v>No maintained-main override.</x:v>
       </x:c>
       <x:c r="F104" s="12" t="str">
-        <x:v>Titan, AlienTitan and AlienMothership accept only FourHull weapons, one per cell. Smaller hull weapons are hidden in icon and table catalogs. Full heavy costs remain. Player and AI share eligibility.</x:v>
+        <x:v>Titan, AlienTitan and AlienMothership accept only FourHull weapons, one per cell. Smaller hull weapons are hidden in icon and table catalogs. Full heavy costs remain. Player and AI share eligibility. Mothership mount positions are symmetric and spaced on verified rim/crown surfaces.</x:v>
       </x:c>
       <x:c r="G104" s="12" t="str">
         <x:v>none</x:v>
       </x:c>
       <x:c r="H104" s="12" t="str">
-        <x:v>CapitalMountPatches.cs:CapitalWeaponFootprintPatch;CapitalMountPatches.cs:CapitalWeaponAvailabilityPatch;CapitalMountPatches.cs:CapitalWeaponAssignmentPatch;CapitalMountPatches.cs:CapitalWeaponDropPatch;CapitalMountPatches.cs:CapitalWeaponIconPatch;CapitalMountPatches.cs:CapitalWeaponModelAnchorPatch;CapitalMountPatches.cs:CapitalAiHullWeaponsPatch;CapitalMountPatches.cs:CapitalNewDesignSchemaPatch;CapitalMountPatches.cs:CapitalCloneSchemaPatch;CapitalMountPatches.cs:CapitalDesignValidationPatch;CapitalMountPatches.cs:CapitalCompleteDesignPatch;CapitalMountPatches.cs:CapitalSavedDesignGuardPatch;CapitalMountPatches.cs:CapitalRefitLayoutGuardPatch;CapitalMountPatches.cs:CapitalImportedDesignPatch;CapitalMountPatches.cs:CapitalWeaponCatalogPatch</x:v>
+        <x:v>CapitalMountPatches.cs:CapitalWeaponFootprintPatch;CapitalMountPatches.cs:CapitalWeaponAvailabilityPatch;CapitalMountPatches.cs:CapitalWeaponAssignmentPatch;CapitalMountPatches.cs:CapitalWeaponDropPatch;CapitalMountPatches.cs:CapitalWeaponIconPatch;CapitalMountPatches.cs:CapitalWeaponModelAnchorPatch;CapitalMountPatches.cs:CapitalAiHullWeaponsPatch;CapitalMountPatches.cs:CapitalNewDesignSchemaPatch;CapitalMountPatches.cs:CapitalCloneSchemaPatch;CapitalMountPatches.cs:CapitalDesignValidationPatch;CapitalMountPatches.cs:CapitalCompleteDesignPatch;CapitalMountPatches.cs:CapitalSavedDesignGuardPatch;CapitalMountPatches.cs:CapitalRefitLayoutGuardPatch;CapitalMountPatches.cs:CapitalImportedDesignPatch;CapitalMountPatches.cs:CapitalWeaponCatalogPatch;MothershipMountPatches.cs:CapitalMothershipGeometryPatch</x:v>
       </x:c>
       <x:c r="I104" s="12" t="str">
         <x:v>implemented</x:v>
       </x:c>
       <x:c r="J104" s="12" t="str">
-        <x:v>0.10.0. Nose fittings and statistics unchanged; maximum-nose proposal deferred. Mothership uses a JSON-only layout inside the native designer grid; no bespoke row code.</x:v>
+        <x:v>Nose fitting unchanged. Mothership retains 16 active hull guns and 8200 t: four extra guns need 42 icons, beyond native capacity. Geometry correction covers 20 authored pairs with guarded, idempotent pre-build placement. In-game validation pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="260" customHeight="1">
@@ -4140,7 +4140,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19c7c870f91347ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree30ea9f3a7b403b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/current-implementation-matrix.xlsx
+++ b/docs/current-implementation-matrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="R85d6809df0054464"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="R37cedeee8b984f8a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -479,8 +479,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImplementationMatrix" displayName="ImplementationMatrix" ref="A1:J107" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:J107"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImplementationMatrix" displayName="ImplementationMatrix" ref="A1:J108" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:J108"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="feature_id"/>
     <x:tableColumn id="2" name="category"/>
@@ -4126,6 +4126,38 @@
         <x:v>Mixed or unowned points block new demands. Native claims and other gates remain. Assume Control and already queued demands are unchanged. See docs/alien-territory-demands.md. Manual testing pending.</x:v>
       </x:c>
     </x:row>
+    <x:row r="108" ht="135" customHeight="1">
+      <x:c r="A108" s="75" t="str">
+        <x:v>ship_gunpowder_canonical_art</x:v>
+      </x:c>
+      <x:c r="B108" s="75" t="str">
+        <x:v>ships</x:v>
+      </x:c>
+      <x:c r="C108" s="75" t="str">
+        <x:v>Canonical gunpowder art</x:v>
+      </x:c>
+      <x:c r="D108" s="75" t="str">
+        <x:v>Shared model scale; previews retain hull placeholders.</x:v>
+      </x:c>
+      <x:c r="E108" s="75" t="str">
+        <x:v>No maintained-main override.</x:v>
+      </x:c>
+      <x:c r="F108" s="75" t="str">
+        <x:v>Eight gunpowder models match canonical bores using cached private mesh copies and scaled pivots/muzzle transforms. Designer/combat dimensions agree. Native state is restored on reuse. Stats and tiers are unchanged.</x:v>
+      </x:c>
+      <x:c r="G108" s="75" t="str">
+        <x:v>shipBalance.enabled</x:v>
+      </x:c>
+      <x:c r="H108" s="75" t="str">
+        <x:v>GunpowderArtPatches.cs:GunpowderArtSetWeaponPatch;GunpowderArtPatches.cs:GunpowderArtRepairMaterialPatch;Core/GunpowderArtCatalog.cs;Core/GunpowderArtGeometry.cs;Config/gunpowder-art-profiles.eeo</x:v>
+      </x:c>
+      <x:c r="I108" s="75" t="str">
+        <x:v>implemented</x:v>
+      </x:c>
+      <x:c r="J108" s="75" t="str">
+        <x:v>0.10.8 accepted by user on 2026-10-21: cutout fixed. Runtime records baked=True, nonInstanced=False. Exact GPU cause unproven. Comparison controls retained for regression testing; lasers/magnetics remain deferred.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="I2:I38">
@@ -4140,7 +4172,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree30ea9f3a7b403b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40dabcace2a64fab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/current-implementation-matrix.xlsx
+++ b/docs/current-implementation-matrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="R37cedeee8b984f8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Matrix" sheetId="1" r:id="R7d4ae8256e784935"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -479,8 +479,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImplementationMatrix" displayName="ImplementationMatrix" ref="A1:J108" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:J108"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImplementationMatrix" displayName="ImplementationMatrix" ref="A1:J120" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:J120"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="feature_id"/>
     <x:tableColumn id="2" name="category"/>
@@ -2814,7 +2814,7 @@
         <x:v>The registry is rebuilt from active load-ordered mod JSON before a save is selected. TI 1.0.51 late saves retain their saved fuel while propulsion is marked for recalculation, and mixed conventional-gun unlock sets initialize without a module-table exception. Disabling or removing the mod requires no custom save payload. TI 1.0.53 faction designs now refresh every performance cache after save registration, preventing one cached statistic from retaining an older mass model.</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" ht="13.5" hidden="0" customHeight="1">
+    <x:row r="67" ht="270" hidden="0" customHeight="1">
       <x:c r="A67" s="11" t="str">
         <x:v>ship_projectile_geometry</x:v>
       </x:c>
@@ -2831,19 +2831,19 @@
         <x:v>No maintained-main override</x:v>
       </x:c>
       <x:c r="F67" s="11" t="str">
-        <x:v>Generic projectileDiameter_mm data sets a caliber-sized collider at ship-model cinematic scale and supplies the matching physical circular cross-section. Conventional diameters are 30, 35, 40, 40, 152.4, 203.2, 254, and 304.8 mm</x:v>
+        <x:v>Completed native movement is the only ballistic flight calculation. Contacts use its actual rendered segment, registered nontrigger geometry and cached visual-mesh refinement. Native damage and lifecycle remain.</x:v>
       </x:c>
       <x:c r="G67" s="11" t="str">
-        <x:v>shipBalance.enabled</x:v>
+        <x:v>shipBalance.enabled;shipBalance.projectileScaleMultiplier</x:v>
       </x:c>
       <x:c r="H67" s="11" t="str">
-        <x:v>TIGunTemplate.json;Core/TemplateFloatExtensionReader.cs;Core/ProjectileGeometryRegistry.cs;Core/ProjectileCollisionMath.cs;ProjectileCollisionPatches.cs:ProjectileColliderSizingPatch;ProjectileCollisionPatches.cs:ProjectileCrossSectionPatch</x:v>
+        <x:v>TIGunTemplate.json;Core/TemplateFloatExtensionReader.cs;Core/ProjectileGeometryRegistry.cs;Core/ProjectileCollisionMath.cs;ProjectileCollisionPatches.cs:ProjectileColliderSizingPatch;ProjectileCollisionPatches.cs:ProjectileCrossSectionPatch;BallisticContactPatches.cs:BallisticCompletedStepRegistrationPatch;BallisticContactPatches.cs:BallisticCompletedStepPhasePatch;BallisticContactPatches.cs:BallisticCompletedStepResolvePatch;BallisticContactPatches.cs:ProjectileRegisteredGeometryFilterPatch</x:v>
       </x:c>
       <x:c r="I67" s="11" t="str">
         <x:v>updated</x:v>
       </x:c>
       <x:c r="J67" s="11" t="str">
-        <x:v>Collider dimensions are assigned absolutely on every pooled projectile fire, so reuse cannot compound scaling. The registry also accepts future TIMagneticGunTemplate diameter fields; no magnetic rows are changed in this pass.</x:v>
+        <x:v>0.10.17 experimental: immutable bone-local rigid/blended contact forests, fitted bone envelopes, shared pose snapshots and body/part rejection. No battle-time skin bake/refit, vertex copy or global physics sync. 15x with 48 arrivals is the runtime acceptance target; synthetic timing is separate. User reports adequate performance in limited 0.10.17 testing; full 15x arrival workload remains unconfirmed.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="13.5" hidden="0" customHeight="1">
@@ -4156,6 +4156,390 @@
       </x:c>
       <x:c r="J108" s="75" t="str">
         <x:v>0.10.8 accepted by user on 2026-10-21: cutout fixed. Runtime records baked=True, nonInstanced=False. Exact GPU cause unproven. Comparison controls retained for regression testing; lasers/magnetics remain deferred.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="270" customHeight="1">
+      <x:c r="A109" s="75" t="str">
+        <x:v>ship_combat_metre_scale</x:v>
+      </x:c>
+      <x:c r="B109" s="75" t="str">
+        <x:v>ships</x:v>
+      </x:c>
+      <x:c r="C109" s="75" t="str">
+        <x:v>Combat metre scale and mesh colliders</x:v>
+      </x:c>
+      <x:c r="D109" s="75" t="str">
+        <x:v>20x/200x ship enlargement; 50x/500x projectile visuals; authored hitbox mismatches.</x:v>
+      </x:c>
+      <x:c r="E109" s="75" t="str">
+        <x:v>Native geometry retained.</x:v>
+      </x:c>
+      <x:c r="F109" s="75" t="str">
+        <x:v>Ship/station and projectile geometry use independent captured settings multipliers. Default 10x/10x means 0.0005 units/metre for both, overriding cinematic geometry policy.</x:v>
+      </x:c>
+      <x:c r="G109" s="75" t="str">
+        <x:v>shipBalance.enabled;shipBalance.shipScaleMultiplier;shipBalance.projectileScaleMultiplier</x:v>
+      </x:c>
+      <x:c r="H109" s="75" t="str">
+        <x:v>BattleGeometryPatches.cs:BattleModelScalePatch;BattleGeometryPatches.cs:BattleProjectileScalePatch;BattleGeometryPatches.cs:BattleGridScalePatch;BattleGeometryPatches.cs:BattleShipBoundsPatch;BattleGeometryPatches.cs:BattleShipGeometryPatch;BattleGeometryPatches.cs:BattleShipGeometryRestorePatch;BattleGeometryPatches.cs:BattleHabGeometryPatch;BattleGeometryPatches.cs:BattleHabGeometryRestorePatch;BattleGeometryPatches.cs:BattleHabFormationGeometryPatch;BattleGeometryPatches.cs:BattleMissileGeometryPatch;BattleGeometryPatches.cs:BattleProjectileHidePatch;BattleGeometryPatches.cs:BattleThreatGeometryPatch;BattleGeometryPatches.cs:BattleMissileSweepPatch;Core/BattleScaleMath.cs;Core/CombatMeshGeometry.cs;Core/BattleProjectileGeometry.cs;ProjectileCollisionPatches.cs:ProjectileColliderSizingPatch</x:v>
+      </x:c>
+      <x:c r="I109" s="75" t="str">
+        <x:v>implemented</x:v>
+      </x:c>
+      <x:c r="J109" s="75" t="str">
+        <x:v>0.10.14: missing/invalid scale settings default to 10. Fresh battle captures values; existing battle remains coherent.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="142.5" customHeight="1">
+      <x:c r="A110" s="75" t="str">
+        <x:v>combat_camera_minimum_speed</x:v>
+      </x:c>
+      <x:c r="B110" s="75" t="str">
+        <x:v>ui</x:v>
+      </x:c>
+      <x:c r="C110" s="75" t="str">
+        <x:v>Minimum combat camera movement and scrolling</x:v>
+      </x:c>
+      <x:c r="D110" s="75" t="str">
+        <x:v>Minimum movement 5; scroll coefficient -200.</x:v>
+      </x:c>
+      <x:c r="E110" s="75" t="str">
+        <x:v>Native camera behavior.</x:v>
+      </x:c>
+      <x:c r="F110" s="75" t="str">
+        <x:v>Packaged 0.25 movement/-10 scroll values remain the 1x reference. Runtime close minima scale with captured ship size and compensate native camera mode.</x:v>
+      </x:c>
+      <x:c r="G110" s="75" t="str">
+        <x:v>shipBalance.enabled;shipBalance.shipScaleMultiplier</x:v>
+      </x:c>
+      <x:c r="H110" s="75" t="str">
+        <x:v>TIGlobalConfig.json;CombatViewPatches.cs:BattleCloseMovementScalePatch;CombatViewPatches.cs:BattleCloseScrollScalePatch</x:v>
+      </x:c>
+      <x:c r="I110" s="75" t="str">
+        <x:v>implemented</x:v>
+      </x:c>
+      <x:c r="J110" s="75" t="str">
+        <x:v>0.10.14: equivalent near-view world controls in both modes at the same ship scale. Far speed values remain native.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="180" customHeight="1">
+      <x:c r="A111" s="75" t="str">
+        <x:v>combat_renderer_mesh_baking</x:v>
+      </x:c>
+      <x:c r="B111" s="75" t="str">
+        <x:v>ships</x:v>
+      </x:c>
+      <x:c r="C111" s="75" t="str">
+        <x:v>Stable ship and station rendering</x:v>
+      </x:c>
+      <x:c r="D111" s="75" t="str">
+        <x:v>Small transform matrices can produce user-observed invisible/cutout solid meshes.</x:v>
+      </x:c>
+      <x:c r="E111" s="75" t="str">
+        <x:v>Native render geometry.</x:v>
+      </x:c>
+      <x:c r="F111" s="75" t="str">
+        <x:v>Private mesh baking uses the captured ship multiplier relative to native renderer scale. Keeps visible geometry/collider fit coherent and stable renderer transforms.</x:v>
+      </x:c>
+      <x:c r="G111" s="75" t="str">
+        <x:v>shipBalance.enabled;shipBalance.shipScaleMultiplier</x:v>
+      </x:c>
+      <x:c r="H111" s="75" t="str">
+        <x:v>CombatViewPatches.cs:BattleHabRenderBakePatch;Core/CombatRenderGeometry.cs;Core/CombatMeshGeometry.cs</x:v>
+      </x:c>
+      <x:c r="I111" s="75" t="str">
+        <x:v>implemented</x:v>
+      </x:c>
+      <x:c r="J111" s="75" t="str">
+        <x:v>0.10.14: arbitrary supported scale values share the existing guarded base/DLC mesh data and exit restoration.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="180" customHeight="1">
+      <x:c r="A112" s="75" t="str">
+        <x:v>combat_path_visual_scale</x:v>
+      </x:c>
+      <x:c r="B112" s="75" t="str">
+        <x:v>ships</x:v>
+      </x:c>
+      <x:c r="C112" s="75" t="str">
+        <x:v>Trajectory thickness and waypoint size</x:v>
+      </x:c>
+      <x:c r="D112" s="75" t="str">
+        <x:v>World-space lines and waypoint minimum/gain retained legacy sizes. Screen-space VectorLine widths are already pixels.</x:v>
+      </x:c>
+      <x:c r="E112" s="75" t="str">
+        <x:v>Native path visual sizing.</x:v>
+      </x:c>
+      <x:c r="F112" s="75" t="str">
+        <x:v>World-space path thickness and waypoint/gizmo gain/minimum share the captured ship scale; already-scaled maximum follows model geometry. Path endpoints/timings are unchanged.</x:v>
+      </x:c>
+      <x:c r="G112" s="75" t="str">
+        <x:v>shipBalance.enabled;shipBalance.shipScaleMultiplier</x:v>
+      </x:c>
+      <x:c r="H112" s="75" t="str">
+        <x:v>CombatViewPatches.cs:BattleWaypointScalePatch;CombatViewPatches.cs:BattlePathThicknessPatch</x:v>
+      </x:c>
+      <x:c r="I112" s="75" t="str">
+        <x:v>implemented</x:v>
+      </x:c>
+      <x:c r="J112" s="75" t="str">
+        <x:v>0.10.14: arrows/gizmos and related 3D UI track the same ship setting. Pixel strokes/text retain their readable units.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="180" customHeight="1">
+      <x:c r="A113" s="75" t="str">
+        <x:v>combat_close_zoom_scale</x:v>
+      </x:c>
+      <x:c r="B113" s="75" t="str">
+        <x:v>ui</x:v>
+      </x:c>
+      <x:c r="C113" s="75" t="str">
+        <x:v>Scaled closest zoom and free-look stop</x:v>
+      </x:c>
+      <x:c r="D113" s="75" t="str">
+        <x:v>Unscaled closest radius; free-look dolly can continue beyond polar-radius clamp. Main/world-UI near clips stay fixed.</x:v>
+      </x:c>
+      <x:c r="E113" s="75" t="str">
+        <x:v>Native camera close limits.</x:v>
+      </x:c>
+      <x:c r="F113" s="75" t="str">
+        <x:v>Close radius, world-camera near planes and dolly standoff share captured ship size. Overshoot protection remains.</x:v>
+      </x:c>
+      <x:c r="G113" s="75" t="str">
+        <x:v>shipBalance.enabled;shipBalance.shipScaleMultiplier</x:v>
+      </x:c>
+      <x:c r="H113" s="75" t="str">
+        <x:v>CombatViewPatches.cs:BattleClosestZoomPatch;CombatViewPatches.cs:BattleCameraClipPatch;CombatViewPatches.cs:BattleCameraClipRestorePatch;CombatViewPatches.cs:BattleDollyStopPatch;Core/CombatViewMath.cs</x:v>
+      </x:c>
+      <x:c r="I113" s="75" t="str">
+        <x:v>implemented</x:v>
+      </x:c>
+      <x:c r="J113" s="75" t="str">
+        <x:v>0.10.14: 10x trial baseline closest orbit 1 km in either cinematic mode, subject to object bounds.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="180" customHeight="1">
+      <x:c r="A114" s="75" t="str">
+        <x:v>combat_projectile_tactical_range</x:v>
+      </x:c>
+      <x:c r="B114" s="75" t="str">
+        <x:v>ships</x:v>
+      </x:c>
+      <x:c r="C114" s="75" t="str">
+        <x:v>Projectile tactical view distance</x:v>
+      </x:c>
+      <x:c r="D114" s="75" t="str">
+        <x:v>Missile tracking symbols switch at a fixed 2 scene units; ballistic effects serve as tracer graphics.</x:v>
+      </x:c>
+      <x:c r="E114" s="75" t="str">
+        <x:v>Native tracking/tracer visuals.</x:v>
+      </x:c>
+      <x:c r="F114" s="75" t="str">
+        <x:v>Tactical-display envelope is 40 km times projectileScaleMultiplier/50, in both cinematic modes; marker angular sizing and physical body/hitbox remain separate.</x:v>
+      </x:c>
+      <x:c r="G114" s="75" t="str">
+        <x:v>shipBalance.enabled;shipBalance.projectileScaleMultiplier</x:v>
+      </x:c>
+      <x:c r="H114" s="75" t="str">
+        <x:v>CombatViewPatches.cs:BattleProjectileTacticalPatch;Core/BattleProjectileGeometry.cs;Core/CombatViewMath.cs</x:v>
+      </x:c>
+      <x:c r="I114" s="75" t="str">
+        <x:v>implemented</x:v>
+      </x:c>
+      <x:c r="J114" s="75" t="str">
+        <x:v>0.10.14: default 10x projectile setting switches at 8 km. Ship setting cannot change this threshold.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="150" customHeight="1">
+      <x:c r="A115" s="75" t="str">
+        <x:v>combat_grid_thickness</x:v>
+      </x:c>
+      <x:c r="B115" s="75" t="str">
+        <x:v>ui</x:v>
+      </x:c>
+      <x:c r="C115" s="75" t="str">
+        <x:v>Combat grid blue-line thickness</x:v>
+      </x:c>
+      <x:c r="D115" s="75" t="str">
+        <x:v>CombatGrid.Update overwrites world-space line thickness independently of trajectory rendering.</x:v>
+      </x:c>
+      <x:c r="E115" s="75" t="str">
+        <x:v>Native grid thickness.</x:v>
+      </x:c>
+      <x:c r="F115" s="75" t="str">
+        <x:v>Blue-grid thickness shares captured ship scale through the common world-UI factor. Endpoints and input-plane reach are retained.</x:v>
+      </x:c>
+      <x:c r="G115" s="75" t="str">
+        <x:v>shipBalance.enabled;shipBalance.shipScaleMultiplier</x:v>
+      </x:c>
+      <x:c r="H115" s="75" t="str">
+        <x:v>CombatSpacingEffectsPatches.cs:BattleGridThicknessPatch</x:v>
+      </x:c>
+      <x:c r="I115" s="75" t="str">
+        <x:v>implemented</x:v>
+      </x:c>
+      <x:c r="J115" s="75" t="str">
+        <x:v>0.10.14: setting-driven, not a fixed 1/20 factor.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="150" customHeight="1">
+      <x:c r="A116" s="75" t="str">
+        <x:v>combat_formation_spacing</x:v>
+      </x:c>
+      <x:c r="B116" s="75" t="str">
+        <x:v>ships</x:v>
+      </x:c>
+      <x:c r="C116" s="75" t="str">
+        <x:v>Formation spacing follows hull scale</x:v>
+      </x:c>
+      <x:c r="D116" s="75" t="str">
+        <x:v>Spacing factor 0.1 physical and 1 cinematic; strategic layer uses its separate unscaled branch.</x:v>
+      </x:c>
+      <x:c r="E116" s="75" t="str">
+        <x:v>Native formation spacing.</x:v>
+      </x:c>
+      <x:c r="F116" s="75" t="str">
+        <x:v>Combat formation factor equals shipScaleMultiplier/200. At 10x, tight spacing is 3/3/5 km in both modes. Strategic offsets and opposing-fleet separation remain native.</x:v>
+      </x:c>
+      <x:c r="G116" s="75" t="str">
+        <x:v>shipBalance.enabled;shipBalance.shipScaleMultiplier</x:v>
+      </x:c>
+      <x:c r="H116" s="75" t="str">
+        <x:v>CombatSpacingEffectsPatches.cs:BattleFormationSpacingPatch</x:v>
+      </x:c>
+      <x:c r="I116" s="75" t="str">
+        <x:v>implemented</x:v>
+      </x:c>
+      <x:c r="J116" s="75" t="str">
+        <x:v>0.10.14: setup/live/reinforcement and disabled/strategic checks cover multiple settings values.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="240" customHeight="1">
+      <x:c r="A117" s="75" t="str">
+        <x:v>combat_explosion_geometry</x:v>
+      </x:c>
+      <x:c r="B117" s="75" t="str">
+        <x:v>ships</x:v>
+      </x:c>
+      <x:c r="C117" s="75" t="str">
+        <x:v>Hull-relative explosion size</x:v>
+      </x:c>
+      <x:c r="D117" s="75" t="str">
+        <x:v>Native VFX cancel parent scale or spawn beneath compensated render transforms.</x:v>
+      </x:c>
+      <x:c r="E117" s="75" t="str">
+        <x:v>Native effect sizing.</x:v>
+      </x:c>
+      <x:c r="F117" s="75" t="str">
+        <x:v>Destruction effects fit visible hull/part dimensions, so they follow captured ship scale. Station observer retains the confirmed startup fix.</x:v>
+      </x:c>
+      <x:c r="G117" s="75" t="str">
+        <x:v>shipBalance.enabled;shipBalance.shipScaleMultiplier</x:v>
+      </x:c>
+      <x:c r="H117" s="75" t="str">
+        <x:v>CombatSpacingEffectsPatches.cs:BattleShipExplosionGeometryPatch;CombatSpacingEffectsPatches.cs:BattleExplosionJitterPatch;CombatSpacingEffectsPatches.cs:BattleRadiatorExplosionGeometryPatch;CombatSpacingEffectsPatches.cs:BattleWeaponExplosionGeometryPatch;CombatSpacingEffectsPatches.cs:BattleStationExplosionGeometryPatch;CombatSpacingEffectsPatches.cs:BattleParticleGroupExplosionPatch;Core/CombatExplosionGeometry.cs</x:v>
+      </x:c>
+      <x:c r="I117" s="75" t="str">
+        <x:v>implemented</x:v>
+      </x:c>
+      <x:c r="J117" s="75" t="str">
+        <x:v>0.10.14: arbitrary parent scale compensation retained; timing/damage ranges unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="240" customHeight="1">
+      <x:c r="A118" s="75" t="str">
+        <x:v>combat_laser_aperture_width</x:v>
+      </x:c>
+      <x:c r="B118" s="75" t="str">
+        <x:v>ships</x:v>
+      </x:c>
+      <x:c r="C118" s="75" t="str">
+        <x:v>Laser ribbon follows visible aperture</x:v>
+      </x:c>
+      <x:c r="D118" s="75" t="str">
+        <x:v>Camera-distance floor widens beams without relation to the emitter opening.</x:v>
+      </x:c>
+      <x:c r="E118" s="75" t="str">
+        <x:v>Native beam width.</x:v>
+      </x:c>
+      <x:c r="F118" s="75" t="str">
+        <x:v>Vanilla LineRenderer, shader, texture, color, width profile and native endpoint updates. Only ribbon width multiplier follows the measured lens; U compensates the ship-scale factor to preserve vanilla longitudinal repeat length. V and offsets stay native.</x:v>
+      </x:c>
+      <x:c r="G118" s="75" t="str">
+        <x:v>shipBalance.enabled;shipBalance.shipScaleMultiplier</x:v>
+      </x:c>
+      <x:c r="H118" s="75" t="str">
+        <x:v>LaserBeamCameraPatches.cs:BattleLaserEmitterPatch;LaserBeamCameraPatches.cs:BattleLaserRibbonPatch;LaserBeamCameraPatches.cs:BattleLaserRibbonRestorePatch;Core/LaserBeamGeometry.cs;Config/laser-beam-optics.eeo</x:v>
+      </x:c>
+      <x:c r="I118" s="75" t="str">
+        <x:v>implemented</x:v>
+      </x:c>
+      <x:c r="J118" s="75" t="str">
+        <x:v>0.10.19 current visual result user-accepted 2026-10-30; documentation/commit/push authorized. Vanilla renderer/profile/endpoints, aperture-only width and vanilla longitudinal repeat retained. Broader scale/asset/pooling matrix and full 15x arrival coverage remain unconfirmed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="180" customHeight="1">
+      <x:c r="A119" s="75" t="str">
+        <x:v>combat_initial_camera_scale</x:v>
+      </x:c>
+      <x:c r="B119" s="75" t="str">
+        <x:v>ui</x:v>
+      </x:c>
+      <x:c r="C119" s="75" t="str">
+        <x:v>Initial camera framing follows hull scale</x:v>
+      </x:c>
+      <x:c r="D119" s="75" t="str">
+        <x:v>400-times-scale orbit and fleet/station offsets remain at legacy scale.</x:v>
+      </x:c>
+      <x:c r="E119" s="75" t="str">
+        <x:v>Native opening camera.</x:v>
+      </x:c>
+      <x:c r="F119" s="75" t="str">
+        <x:v>Initial camera orbit and fleet/station offsets share captured ship scale. Default 10x gives 20 km orbit baseline in either cinematic mode.</x:v>
+      </x:c>
+      <x:c r="G119" s="75" t="str">
+        <x:v>shipBalance.enabled;shipBalance.shipScaleMultiplier</x:v>
+      </x:c>
+      <x:c r="H119" s="75" t="str">
+        <x:v>LaserBeamCameraPatches.cs:BattleInitialCameraScalePatch</x:v>
+      </x:c>
+      <x:c r="I119" s="75" t="str">
+        <x:v>implemented</x:v>
+      </x:c>
+      <x:c r="J119" s="75" t="str">
+        <x:v>0.10.14: close and opening camera scale coherently; far viewing limits retained.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="180" customHeight="1">
+      <x:c r="A120" s="75" t="str">
+        <x:v>combat_settings_scale</x:v>
+      </x:c>
+      <x:c r="B120" s="75" t="str">
+        <x:v>ships</x:v>
+      </x:c>
+      <x:c r="C120" s="75" t="str">
+        <x:v>Configurable ship and projectile combat scale</x:v>
+      </x:c>
+      <x:c r="D120" s="75" t="str">
+        <x:v>Native cinematic toggle selects fixed model/projectile factors.</x:v>
+      </x:c>
+      <x:c r="E120" s="75" t="str">
+        <x:v>Native fixed factors.</x:v>
+      </x:c>
+      <x:c r="F120" s="75" t="str">
+        <x:v>Independent settings default to 10x/10x, range 0.01-1000, override cinematic geometry size. Captured at battle initialization and released on exit; edits apply next battle. Older XML retains constructor defaults.</x:v>
+      </x:c>
+      <x:c r="G120" s="75" t="str">
+        <x:v>shipBalance.enabled;shipBalance.shipScaleMultiplier;shipBalance.projectileScaleMultiplier</x:v>
+      </x:c>
+      <x:c r="H120" s="75" t="str">
+        <x:v>BattleGeometryPatches.cs:BattleScaleSettingsCapturePatch;Core/BattleScaleMath.cs;Core/CombatViewMath.cs;Main.cs;Settings.xml</x:v>
+      </x:c>
+      <x:c r="I120" s="75" t="str">
+        <x:v>implemented</x:v>
+      </x:c>
+      <x:c r="J120" s="75" t="str">
+        <x:v>0.10.14 testing build. Shared model/projectile sources feed all prior dimensional fixes. Values remain per-battle snapshots to avoid mixed scales.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4172,7 +4556,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40dabcace2a64fab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R588210bb21d44a44"/>
   </x:tableParts>
 </x:worksheet>
 </file>